--- a/ftse250_weekly_summary_2026-10-13.xlsx
+++ b/ftse250_weekly_summary_2026-10-13.xlsx
@@ -456,555 +456,639 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SNR.L</t>
+          <t>GNC.L</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Senior plc</t>
+          <t>Greencore Group plc</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.34</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>297.5</v>
+        <v>268.4</v>
       </c>
       <c r="E2" t="n">
-        <v>296.5</v>
+        <v>245.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>5535227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AML.L</t>
+          <t>HBR.L</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aston Martin Lagonda global Holdings plc</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>Harbour Energy plc</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>291.8</v>
+      </c>
       <c r="E3" t="n">
-        <v>36.1</v>
+        <v>267.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>194787</v>
+        <v>3984063</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASC.L</t>
+          <t>BP.L</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ardmore Shipping Corporation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>BP p.l.c.</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D4" t="n">
+        <v>610</v>
+      </c>
       <c r="E4" t="n">
-        <v>502</v>
+        <v>560.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>107356</v>
+        <v>52576615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ATG.L</t>
+          <t>ITH.L</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Auction Technology Group plc</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>Ithaca Energy plc</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="D5" t="n">
+        <v>294.2</v>
+      </c>
       <c r="E5" t="n">
-        <v>458.2</v>
+        <v>274.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>25831</v>
+        <v>1445938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAB.L</t>
+          <t>ENOG.L</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Babcock International Group PLC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Energean plc</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>747</v>
+      </c>
       <c r="E6" t="n">
-        <v>925.8</v>
+        <v>696.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>222757</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BAG.L</t>
+          <t>TRN.L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A.G. BARR p.l.c.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>Trainline Plc</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="D7" t="n">
+        <v>210.4</v>
+      </c>
       <c r="E7" t="n">
-        <v>547</v>
+        <v>196.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>55271</v>
+        <v>579434</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BBY.L</t>
+          <t>DEC.L</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Balfour Beatty plc</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>Diversified Energy Company PLC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1116</v>
+      </c>
       <c r="E8" t="n">
-        <v>911</v>
+        <v>1044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>60780</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BOY.L</t>
+          <t>STEM.L</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bodycote plc</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>SThree plc</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="D9" t="n">
+        <v>311</v>
+      </c>
       <c r="E9" t="n">
-        <v>910.5</v>
+        <v>293.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>850035</v>
+        <v>294955</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BP.L</t>
+          <t>SHEL.L</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BP p.l.c.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>Shell plc</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3865.5</v>
+      </c>
       <c r="E10" t="n">
-        <v>563.2</v>
+        <v>3651</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>160</v>
+        <v>6782922</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BREE.L</t>
+          <t>AML.L</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Breedon Group plc</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>Aston Martin Lagonda global Holdings plc</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="D11" t="n">
+        <v>37.22</v>
+      </c>
       <c r="E11" t="n">
-        <v>311.2</v>
+        <v>35.44</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>175497</v>
+        <v>5802063</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BWY.L</t>
+          <t>PFD.L</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bellway p.l.c.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>Premier Foods plc</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>197.3</v>
+      </c>
       <c r="E12" t="n">
-        <v>2038</v>
+        <v>188</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>234732</v>
+        <v>1805578</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CCR.L</t>
+          <t>JDW.L</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C&amp;C Group plc</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>J D Wetherspoon plc</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1008</v>
+      </c>
       <c r="E13" t="n">
-        <v>96.3</v>
+        <v>962.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1295</v>
+        <v>279568</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CHG.L</t>
+          <t>MOON.L</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chemring Group PLC</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>Moonpig Group plc</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="D14" t="n">
+        <v>282.6</v>
+      </c>
       <c r="E14" t="n">
-        <v>532</v>
+        <v>270.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>387917</v>
+        <v>709315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CKN.L</t>
+          <t>GRG.L</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clarkson PLC</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>Greggs plc</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2142</v>
+      </c>
       <c r="E15" t="n">
-        <v>5050</v>
+        <v>2050</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>486</v>
+        <v>342175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COA.L</t>
+          <t>DNLM.L</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coats Group plc</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>Dunelm Group plc</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="D16" t="n">
+        <v>815.5</v>
+      </c>
       <c r="E16" t="n">
-        <v>80.8</v>
+        <v>780.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>854098</v>
+        <v>300568</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CRST.L</t>
+          <t>HTG.L</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crest Nicholson Holdings plc</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>Hunting PLC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>403.5</v>
+      </c>
       <c r="E17" t="n">
-        <v>58.3</v>
+        <v>386.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>426761</v>
+        <v>744608</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CURY.L</t>
+          <t>MGAM.L</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Currys plc</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>Morgan Advanced Materials plc</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="D18" t="n">
+        <v>288</v>
+      </c>
       <c r="E18" t="n">
-        <v>146.1</v>
+        <v>276.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>6505</v>
+        <v>363363</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CWK.L</t>
+          <t>DOCS.L</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cranswick plc</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>Dr. Martens plc</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="D19" t="n">
+        <v>68.90000000000001</v>
+      </c>
       <c r="E19" t="n">
-        <v>4955</v>
+        <v>66.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7050</v>
+        <v>454002</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CWR.L</t>
+          <t>SRP.L</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ceres Power Holdings plc</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>Serco Group plc</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="D20" t="n">
+        <v>259.2</v>
+      </c>
       <c r="E20" t="n">
-        <v>415</v>
+        <v>249.8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>35000</v>
+        <v>1001598</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DEC.L</t>
+          <t>COA.L</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Diversified Energy Company PLC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>Coats Group plc</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>84.09999999999999</v>
+      </c>
       <c r="E21" t="n">
-        <v>1030</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>336</v>
+        <v>4350766</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DNLM.L</t>
+          <t>CWK.L</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dunelm Group plc</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>Cranswick plc</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5150</v>
+      </c>
       <c r="E22" t="n">
-        <v>775.5</v>
+        <v>4980</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>11323</v>
+        <v>166145</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DOCS.L</t>
+          <t>FGP.L</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dr. Martens plc</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>FirstGroup plc</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="D23" t="n">
+        <v>193.9</v>
+      </c>
       <c r="E23" t="n">
-        <v>66.2</v>
+        <v>187.6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>215371</v>
+        <v>848925</v>
       </c>
     </row>
     <row r="24">
@@ -1018,943 +1102,1095 @@
           <t>Domino's Pizza Group plc</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D24" t="n">
+        <v>230</v>
+      </c>
       <c r="E24" t="n">
-        <v>212.4</v>
+        <v>222.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4324</v>
+        <v>1062930</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DSCV.L</t>
+          <t>PETS.L</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>discoverIE Group plc</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>Pets at Home Group Plc</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D25" t="n">
+        <v>211.8</v>
+      </c>
       <c r="E25" t="n">
-        <v>858</v>
+        <v>205.8</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>66960</v>
+        <v>512301</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ELM.L</t>
+          <t>ATG.L</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Elementis plc</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+          <t>Auction Technology Group plc</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="D26" t="n">
+        <v>479.4</v>
+      </c>
       <c r="E26" t="n">
-        <v>179.4</v>
+        <v>465.8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>605134</v>
+        <v>382905</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENOG.L</t>
+          <t>RHIM.L</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Energean plc</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>RHI Magnesita N.V.</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2925</v>
+      </c>
       <c r="E27" t="n">
-        <v>711.5</v>
+        <v>2845</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>200</v>
+        <v>15970</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ESNT.L</t>
+          <t>CKN.L</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Essentra plc</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+          <t>Clarkson PLC</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5300</v>
+      </c>
       <c r="E28" t="n">
-        <v>111.8</v>
+        <v>5160</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>69424</v>
+        <v>30157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EVOK.L</t>
+          <t>VSVS.L</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>evoke plc</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>Vesuvius plc</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="D29" t="n">
+        <v>457</v>
+      </c>
       <c r="E29" t="n">
-        <v>43.1</v>
+        <v>446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>218697</v>
+        <v>380750</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EZJ.L</t>
+          <t>MAB.L</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>easyJet plc</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+          <t>Mitchells &amp; Butlers plc</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="D30" t="n">
+        <v>294.5</v>
+      </c>
       <c r="E30" t="n">
-        <v>677</v>
+        <v>287.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>525566</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FAN.L</t>
+          <t>CRST.L</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Volution Group plc</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+          <t>Crest Nicholson Holdings plc</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D31" t="n">
+        <v>60.9</v>
+      </c>
       <c r="E31" t="n">
-        <v>647</v>
+        <v>59.7</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>343677</v>
+        <v>1193400</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FGP.L</t>
+          <t>JMAT.L</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FirstGroup plc</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+          <t>Johnson Matthey Plc</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2482</v>
+      </c>
       <c r="E32" t="n">
-        <v>186.4</v>
+        <v>2436</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>90231</v>
+        <v>383077</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FXPO.L</t>
+          <t>GDWN.L</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ferrexpo plc</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>Goodwin PLC</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D33" t="n">
+        <v>14080</v>
+      </c>
       <c r="E33" t="n">
-        <v>32.5</v>
+        <v>13840</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>82928</v>
+        <v>15040</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GAW.L</t>
+          <t>DSCV.L</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Games Workshop Group PLC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+          <t>discoverIE Group plc</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D34" t="n">
+        <v>880</v>
+      </c>
       <c r="E34" t="n">
-        <v>16970</v>
+        <v>865</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>295412</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GDWN.L</t>
+          <t>VCT.L</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Goodwin PLC</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+          <t>Victrex plc</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="D35" t="n">
+        <v>942</v>
+      </c>
       <c r="E35" t="n">
-        <v>13900</v>
+        <v>930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2441</v>
+        <v>131416</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GEN.L</t>
+          <t>MEGP.L</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Genuit Group plc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+          <t>ME Group International plc</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D36" t="n">
+        <v>117</v>
+      </c>
       <c r="E36" t="n">
-        <v>285.4</v>
+        <v>115.6</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>204394</v>
+        <v>2880992</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GFTU.L</t>
+          <t>SMWH.L</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grafton Group plc</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+          <t>WH Smith PLC</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D37" t="n">
+        <v>373.2</v>
+      </c>
       <c r="E37" t="n">
-        <v>933.5</v>
+        <v>369</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>151678</v>
+        <v>379137</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GNC.L</t>
+          <t>PZC.L</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Greencore Group plc</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+          <t>PZ Cussons Plc</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="D38" t="n">
+        <v>97.5</v>
+      </c>
       <c r="E38" t="n">
-        <v>244</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>233000</v>
+        <v>198974</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GRG.L</t>
+          <t>MCG.L</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Greggs plc</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>Mobico Group Plc</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D39" t="n">
+        <v>23.48</v>
+      </c>
       <c r="E39" t="n">
-        <v>2016</v>
+        <v>23.26</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>29</v>
+        <v>3712205</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HAS.L</t>
+          <t>ROR.L</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hays plc</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+          <t>Rotork plc</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D40" t="n">
+        <v>493</v>
+      </c>
       <c r="E40" t="n">
-        <v>62.85</v>
+        <v>488.4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1875474</v>
+        <v>1649953</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HBR.L</t>
+          <t>QQ.L</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Harbour Energy plc</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+          <t>QinetiQ Group plc</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D41" t="n">
+        <v>453.8</v>
+      </c>
       <c r="E41" t="n">
-        <v>273</v>
+        <v>449.8</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>415</v>
+        <v>994699</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HFG.L</t>
+          <t>WOSG.L</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hilton Food Group plc</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+          <t>Watches of Switzerland Group plc</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>673.5</v>
+      </c>
       <c r="E42" t="n">
-        <v>695</v>
+        <v>669.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1301</v>
+        <v>156799</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HILS.L</t>
+          <t>GEN.L</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Hill &amp; Smith PLC</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+          <t>Genuit Group plc</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D43" t="n">
+        <v>287.6</v>
+      </c>
       <c r="E43" t="n">
-        <v>3295</v>
+        <v>286.2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>584350</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HTG.L</t>
+          <t>ESNT.L</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hunting PLC</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+          <t>Essentra plc</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D44" t="n">
+        <v>114.6</v>
+      </c>
       <c r="E44" t="n">
-        <v>394.5</v>
+        <v>114.2</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>38645</v>
+        <v>1278735</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IBST.L</t>
+          <t>ZIG.L</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ibstock plc</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+          <t>Zigup Plc</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D45" t="n">
+        <v>441</v>
+      </c>
       <c r="E45" t="n">
-        <v>79</v>
+        <v>439.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>257521</v>
+        <v>399733</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>INCH.L</t>
+          <t>SNR.L</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Inchcape plc</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>Senior plc</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D46" t="n">
+        <v>297.5</v>
+      </c>
       <c r="E46" t="n">
-        <v>731.5</v>
+        <v>296.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-08 00:00:00</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ITH.L</t>
+          <t>TATE.L</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ithaca Energy plc</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+          <t>Tate &amp; Lyle plc</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D47" t="n">
+        <v>562.5</v>
+      </c>
       <c r="E47" t="n">
-        <v>281.4</v>
+        <v>561</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>2738282</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JDW.L</t>
+          <t>ELM.L</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>J D Wetherspoon plc</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+          <t>Elementis plc</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D48" t="n">
+        <v>181</v>
+      </c>
       <c r="E48" t="n">
-        <v>952.5</v>
+        <v>180.6</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>66091</v>
+        <v>670211</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JMAT.L</t>
+          <t>GFTU.L</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Johnson Matthey Plc</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+          <t>Grafton Group plc</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>943.7</v>
+      </c>
       <c r="E49" t="n">
-        <v>2406</v>
+        <v>941.8</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6044</v>
+        <v>573043</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KLR.L</t>
+          <t>MTO.L</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Keller Group plc</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>Mitie Group plc</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D50" t="n">
+        <v>210.4</v>
+      </c>
       <c r="E50" t="n">
-        <v>3280</v>
+        <v>210</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>7400</v>
+        <v>1777810</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MAB.L</t>
+          <t>KLR.L</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mitchells &amp; Butlers plc</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+          <t>Keller Group plc</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3264</v>
+      </c>
       <c r="E51" t="n">
-        <v>294.5</v>
+        <v>3258</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>66459</v>
+        <v>96703</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MCG.L</t>
+          <t>CURY.L</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mobico Group Plc</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+          <t>Currys plc</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D52" t="n">
+        <v>145.1</v>
+      </c>
       <c r="E52" t="n">
-        <v>23.3</v>
+        <v>144.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>174133</v>
+        <v>2269338</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MEGP.L</t>
+          <t>HFG.L</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ME Group International plc</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+          <t>Hilton Food Group plc</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D53" t="n">
+        <v>714</v>
+      </c>
       <c r="E53" t="n">
-        <v>117.2</v>
+        <v>713.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>40000</v>
+        <v>602393</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MGAM.L</t>
+          <t>BOY.L</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Morgan Advanced Materials plc</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>Bodycote plc</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>910</v>
+      </c>
       <c r="E54" t="n">
-        <v>271</v>
+        <v>910</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>233269</v>
+        <v>1534199</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MGNS.L</t>
+          <t>GAW.L</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Morgan Sindall Group plc</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+          <t>Games Workshop Group PLC</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16550</v>
+      </c>
       <c r="E55" t="n">
-        <v>4172</v>
+        <v>16560</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>15074</v>
+        <v>74989</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MOON.L</t>
+          <t>TPK.L</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Moonpig Group plc</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+          <t>Travis Perkins plc</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="D56" t="n">
+        <v>571</v>
+      </c>
       <c r="E56" t="n">
-        <v>268.4</v>
+        <v>572.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>223277</v>
+        <v>1459156</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MSLH.L</t>
+          <t>BAG.L</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marshalls plc</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>A.G. BARR p.l.c.</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="D57" t="n">
+        <v>556</v>
+      </c>
       <c r="E57" t="n">
-        <v>167.5</v>
+        <v>558</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1680</v>
+        <v>137711</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MTO.L</t>
+          <t>EZJ.L</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mitie Group plc</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>easyJet plc</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="D58" t="n">
+        <v>675</v>
+      </c>
       <c r="E58" t="n">
-        <v>210</v>
+        <v>678.2</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>157</v>
+        <v>2590729</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PAGE.L</t>
+          <t>IBST.L</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PageGroup plc</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+          <t>Ibstock plc</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="D59" t="n">
+        <v>79.09999999999999</v>
+      </c>
       <c r="E59" t="n">
-        <v>208</v>
+        <v>79.55</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2899</v>
+        <v>2412704</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PETS.L</t>
+          <t>ASC.L</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pets at Home Group Plc</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>Ardmore Shipping Corporation</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="D60" t="n">
+        <v>451</v>
+      </c>
       <c r="E60" t="n">
-        <v>206.2</v>
+        <v>454</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>69</v>
+        <v>368784</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PFD.L</t>
+          <t>BREE.L</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Premier Foods plc</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+          <t>Breedon Group plc</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>305.6</v>
+      </c>
       <c r="E61" t="n">
-        <v>186.7</v>
+        <v>309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>8433</v>
+        <v>228383</v>
       </c>
     </row>
     <row r="62">
@@ -1968,500 +2204,584 @@
           <t>Persimmon Plc</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1220.5</v>
+      </c>
       <c r="E62" t="n">
-        <v>1212.5</v>
+        <v>1240</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>50000</v>
+        <v>1253325</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PTEC.L</t>
+          <t>INCH.L</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Playtech plc</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+          <t>Inchcape plc</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="D63" t="n">
+        <v>674.5</v>
+      </c>
       <c r="E63" t="n">
-        <v>386.8</v>
+        <v>686</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>588</v>
+        <v>944247</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PZC.L</t>
+          <t>CHG.L</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PZ Cussons Plc</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+          <t>Chemring Group PLC</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="D64" t="n">
+        <v>499.8</v>
+      </c>
       <c r="E64" t="n">
-        <v>95.2</v>
+        <v>508.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>58424</v>
+        <v>409498</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QQ.L</t>
+          <t>CCR.L</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>QinetiQ Group plc</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+          <t>C&amp;C Group plc</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="D65" t="n">
+        <v>95.59999999999999</v>
+      </c>
       <c r="E65" t="n">
-        <v>475.4</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>269294</v>
+        <v>681397</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RHIM.L</t>
+          <t>FAN.L</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RHI Magnesita N.V.</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+          <t>Volution Group plc</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="D66" t="n">
+        <v>646</v>
+      </c>
       <c r="E66" t="n">
-        <v>2880</v>
+        <v>660</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3151</v>
+        <v>569432</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ROR.L</t>
+          <t>BAB.L</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rotork plc</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+          <t>Babcock International Group PLC</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="D67" t="n">
+        <v>887.2</v>
+      </c>
       <c r="E67" t="n">
-        <v>488.6</v>
+        <v>906.6</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>226689</v>
+        <v>1727894</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SHEL.L</t>
+          <t>MSLH.L</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shell plc</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+          <t>Marshalls plc</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="D68" t="n">
+        <v>163.7</v>
+      </c>
       <c r="E68" t="n">
-        <v>3631.5</v>
+        <v>167.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>140</v>
+        <v>1191740</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SMWH.L</t>
+          <t>EVOK.L</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WH Smith PLC</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+          <t>evoke plc</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="D69" t="n">
+        <v>42</v>
+      </c>
       <c r="E69" t="n">
-        <v>369</v>
+        <v>43</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>606</v>
+        <v>620228</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SRP.L</t>
+          <t>WIZZ.L</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Serco Group plc</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+          <t>Wizz Air Holdings Plc</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1007</v>
+      </c>
       <c r="E70" t="n">
-        <v>252</v>
+        <v>1047</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1839</v>
+        <v>507870</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SSPG.L</t>
+          <t>BWY.L</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SSP Group plc</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+          <t>Bellway p.l.c.</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1956</v>
+      </c>
       <c r="E71" t="n">
-        <v>187.5</v>
+        <v>2044</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>738647</v>
+        <v>849228</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STEM.L</t>
+          <t>PTEC.L</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SThree plc</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+          <t>Playtech plc</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="D72" t="n">
+        <v>362.6</v>
+      </c>
       <c r="E72" t="n">
-        <v>294</v>
+        <v>382.8</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>19</v>
+        <v>166491</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TATE.L</t>
+          <t>BBY.L</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tate &amp; Lyle plc</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+          <t>Balfour Beatty plc</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="D73" t="n">
+        <v>849</v>
+      </c>
       <c r="E73" t="n">
-        <v>559.5</v>
+        <v>900</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>964135</v>
+        <v>2555564</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TPK.L</t>
+          <t>MGNS.L</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Travis Perkins plc</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+          <t>Morgan Sindall Group plc</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3954</v>
+      </c>
       <c r="E74" t="n">
-        <v>579</v>
+        <v>4200</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>245109</v>
+        <v>98533</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TRN.L</t>
+          <t>VTY.L</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trainline Plc</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+          <t>Vistry Group PLC</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="D75" t="n">
+        <v>221.2</v>
+      </c>
       <c r="E75" t="n">
-        <v>194.7</v>
+        <v>236.6</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>297833</v>
+        <v>2267012</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TUI1.DE</t>
+          <t>HILS.L</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TUI AG</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+          <t>Hill &amp; Smith PLC</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3040</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3255</v>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1873622</v>
+        <v>159321</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VCT.L</t>
+          <t>FXPO.L</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Victrex plc</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+          <t>Ferrexpo plc</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>-6.97</v>
+      </c>
+      <c r="D77" t="n">
+        <v>30.68</v>
+      </c>
       <c r="E77" t="n">
-        <v>930</v>
+        <v>32.98</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>315</v>
+        <v>461599</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VSVS.L</t>
+          <t>SSPG.L</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vesuvius plc</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+          <t>SSP Group plc</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>-7.83</v>
+      </c>
+      <c r="D78" t="n">
+        <v>174.1</v>
+      </c>
       <c r="E78" t="n">
-        <v>444.2</v>
+        <v>188.9</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>137142</v>
+        <v>1010239</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VTY.L</t>
+          <t>PAGE.L</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vistry Group PLC</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+          <t>PageGroup plc</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="D79" t="n">
+        <v>192.3</v>
+      </c>
       <c r="E79" t="n">
-        <v>238.8</v>
+        <v>211.4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>828</v>
+        <v>1012540</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WIZZ.L</t>
+          <t>CWR.L</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wizz Air Holdings Plc</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+          <t>Ceres Power Holdings plc</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="D80" t="n">
+        <v>372</v>
+      </c>
       <c r="E80" t="n">
-        <v>1039</v>
+        <v>411.6</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>4</v>
+        <v>2542769</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WOSG.L</t>
+          <t>HAS.L</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Watches of Switzerland Group plc</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+          <t>Hays plc</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>-11.06</v>
+      </c>
+      <c r="D81" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="E81" t="n">
+        <v>62.85</v>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>81125</v>
+        <v>7273693</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ZIG.L</t>
+          <t>TUI1.DE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zigup Plc</t>
+          <t>TUI AG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2469,11 +2789,11 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-10-12 00:00:00</t>
+          <t>2026-10-13 00:00:00</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3980</v>
+        <v>1158967</v>
       </c>
     </row>
   </sheetData>
